--- a/assets/suivi-devis-depart-en.xlsx
+++ b/assets/suivi-devis-depart-en.xlsx
@@ -25,13 +25,13 @@
     <t>Accepted quotes</t>
   </si>
   <si>
-    <t>Total incl. VAT</t>
+    <t>Total with tax</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>Accepted incl. VAT</t>
+    <t>Accepted with tax</t>
   </si>
   <si>
     <t>Declined</t>
@@ -49,13 +49,13 @@
     <t>Validity (days)</t>
   </si>
   <si>
-    <t>Amount excl. VAT</t>
-  </si>
-  <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <t>Amount incl. VAT</t>
+    <t>Amount before tax</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>Amount with tax</t>
   </si>
   <si>
     <t>Deadline</t>
@@ -605,7 +605,7 @@
         <v>2440</v>
       </c>
       <c r="F8">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I8" t="s">
         <v>7</v>
@@ -631,7 +631,7 @@
         <v>1265</v>
       </c>
       <c r="F9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I9" t="s">
         <v>20</v>
@@ -657,7 +657,7 @@
         <v>1890</v>
       </c>
       <c r="F10">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I10" t="s">
         <v>20</v>
@@ -683,7 +683,7 @@
         <v>246</v>
       </c>
       <c r="F11">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I11" t="s">
         <v>5</v>
@@ -706,7 +706,7 @@
         <v>452.5</v>
       </c>
       <c r="F12">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I12" t="s">
         <v>7</v>
@@ -729,7 +729,7 @@
         <v>3200</v>
       </c>
       <c r="F13">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I13" t="s">
         <v>5</v>
@@ -752,7 +752,7 @@
         <v>980</v>
       </c>
       <c r="F14">
-        <v>0.055</v>
+        <v>0.13</v>
       </c>
       <c r="I14" t="s">
         <v>20</v>
@@ -775,7 +775,7 @@
         <v>1500</v>
       </c>
       <c r="F15">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I15" t="s">
         <v>5</v>
@@ -798,7 +798,7 @@
         <v>610</v>
       </c>
       <c r="F16">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I16" t="s">
         <v>7</v>
@@ -821,7 +821,7 @@
         <v>2150</v>
       </c>
       <c r="F17">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="I17" t="s">
         <v>5</v>
